--- a/test-data/RD_Jachymov_dum/outputs/ATOMIC_FLAT_2026-06-02.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/ATOMIC_FLAT_2026-06-02.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ATOMIC_FLAT" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ATOMIC_FLAT'!$A$1:$M$361</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ATOMIC_FLAT'!$A$1:$M$366</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M361"/>
+  <dimension ref="A1:M366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1714,11 +1714,11 @@
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>2.64</v>
+        <v>3.54</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>podlaha sklad 17.6 m² (legenda místností) × 0.15 m podkladní kamenná drť</t>
+          <t>S01 plocha 23.6 m² (místnost 17.6 + vynos za stěnu 6.0 dle řezu) × 0.15 m podkladní drť 4-8 = 3.54 m³</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>DXF podlaha skladu 6.35×3.34 = 21.2 m²</t>
+          <t>legenda místností 17.6 m² + vynos S01 za stěnu 6010×1000 mm dle řezu B-B (neviditelný na půdorysu)</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Montáž — Obvodové stěny skladu — tvarovky ztraceného bednění tl. 250 mm × výška 2.4 m + zalití C25/30</t>
+          <t>Montáž — Obvodové stěny skladu S03a/b — tvarovky ztraceného bednění tl. 250 mm, výška 14 řad × 250 = 3.5 m + zalití C25/30</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -4018,11 +4018,11 @@
         </is>
       </c>
       <c r="H60" s="2" t="n">
-        <v>46.5</v>
+        <v>62.5</v>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>obvod 19.4 m × výška 2.4 m = 46.6</t>
+          <t>3 strany trapézu (6010-1000 dveře)+(7000-600 prefa)+(7033-600 prefa)=17843 mm = 17.84 m × výška 14 řad×0.25 = 3.5 m = 62.5 m²</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 + DXF DIMENSION obvod</t>
+          <t>výkres D.1.1.02/03 — 14 řad tvárnic × 250 mm (řady začínají pod úrovní podlahy od pasu); světlá 2.68 je vnitřní svět, NE výška tvárnic</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>Dodávka — Pronájem bednění (Obvodové stěny skladu — tvarovky ztraceného be)</t>
+          <t>Dodávka — Pronájem bednění (Obvodové stěny skladu S03a/b — tvarovky ztrace)</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="H61" s="2" t="n">
-        <v>46.5</v>
+        <v>62.5</v>
       </c>
       <c r="I61" s="3">
         <f> montáž 1:1</f>
@@ -4090,7 +4090,7 @@
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 + DXF DIMENSION obvod</t>
+          <t>výkres D.1.1.02/03 — 14 řad tvárnic × 250 mm (řady začínají pod úrovní podlahy od pasu); světlá 2.68 je vnitřní svět, NE výška tvárnic</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
@@ -4139,11 +4139,11 @@
         </is>
       </c>
       <c r="H62" s="2" t="n">
-        <v>1398</v>
+        <v>1875</v>
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>46.6 × 30 kg/m² = 1398</t>
+          <t>62.5 m² × 30 kg/m² (zalití C25/30) = 1875 kg</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -4151,10 +4151,9 @@
           <t>273361821</t>
         </is>
       </c>
-      <c r="K62" s="3" t="inlineStr">
-        <is>
-          <t>B4_productivity Methvin — výztuž do ZB tvarovek tl. 250 mm</t>
-        </is>
+      <c r="K62" s="3">
+        <f> HSV3.002 plocha (62.5 m²) × 30 kg/m²</f>
+        <v/>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
@@ -4202,17 +4201,16 @@
         </is>
       </c>
       <c r="H63" s="2" t="n">
-        <v>1398</v>
+        <v>1875</v>
       </c>
       <c r="I63" s="3">
         <f> montáž 1:1</f>
         <v/>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
-      <c r="K63" s="3" t="inlineStr">
-        <is>
-          <t>B4_productivity Methvin — výztuž do ZB tvarovek tl. 250 mm</t>
-        </is>
+      <c r="K63" s="3">
+        <f> HSV3.002 plocha (62.5 m²) × 30 kg/m²</f>
+        <v/>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
@@ -13739,7 +13737,7 @@
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>Betonová dlažba do pískového lože — povrch podlahy skladu (~21 m²)</t>
+          <t>Betonová dlažba 50 mm do kladecího lože — podlaha skladu + vynos za stěnu</t>
         </is>
       </c>
       <c r="G226" s="2" t="inlineStr">
@@ -13748,17 +13746,17 @@
         </is>
       </c>
       <c r="H226" s="2" t="n">
-        <v>17.6</v>
+        <v>23.6</v>
       </c>
       <c r="I226" s="3" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností room 0.01 (sklad zahradní techniky) = 17.60 m² (inner usable area per DXF room table, walls excluded). Prior estimate 21.209 m² (outer 6.35×3.34) over-counted by 17.0% — walls of tvarovky ZB tl. 250 mm take ~3.6 m² of outer footprint.</t>
+          <t>plocha S01 = místnost 17.6 (legenda) + vynos za stěnu 6.0 (6010×1000 řez) = 23.6 m²</t>
         </is>
       </c>
       <c r="J226" s="2" t="inlineStr"/>
       <c r="K226" s="3" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
+          <t>legenda místností 17.6 + vynos S01 za stěnu (řez B-B)</t>
         </is>
       </c>
       <c r="L226" s="2" t="inlineStr">
@@ -21604,8 +21602,294 @@
         </is>
       </c>
     </row>
+    <row r="362">
+      <c r="A362" s="2" t="n">
+        <v>361</v>
+      </c>
+      <c r="B362" s="2" t="inlineStr">
+        <is>
+          <t>HSV1.007</t>
+        </is>
+      </c>
+      <c r="C362" s="2" t="inlineStr">
+        <is>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="D362" s="2" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
+        </is>
+      </c>
+      <c r="E362" s="3" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
+        </is>
+      </c>
+      <c r="F362" s="3" t="inlineStr">
+        <is>
+          <t>Kladecí lože z kamenné drti 4-8 mm tl. 40 mm pod betonovou dlažbu skladu</t>
+        </is>
+      </c>
+      <c r="G362" s="2" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H362" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="I362" s="3" t="inlineStr">
+        <is>
+          <t>S01 plocha 23.6 m² × 0.04 m = 0.94 m³</t>
+        </is>
+      </c>
+      <c r="J362" s="2" t="inlineStr">
+        <is>
+          <t>564231111</t>
+        </is>
+      </c>
+      <c r="K362" s="3" t="inlineStr">
+        <is>
+          <t>skladba S01 — kladecí vrstva kamenná drť 4-8 mm 40 mm (vrstva dříve chyběla)</t>
+        </is>
+      </c>
+      <c r="L362" s="2" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M362" s="2" t="inlineStr">
+        <is>
+          <t>S01_sklad</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="n">
+        <v>362</v>
+      </c>
+      <c r="B363" s="2" t="inlineStr">
+        <is>
+          <t>HSV1.008</t>
+        </is>
+      </c>
+      <c r="C363" s="2" t="inlineStr">
+        <is>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="D363" s="2" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
+        </is>
+      </c>
+      <c r="E363" s="3" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
+        </is>
+      </c>
+      <c r="F363" s="3" t="inlineStr">
+        <is>
+          <t>Zásyp za prefabrikovanou opěrnou stěnou S04 — materiál dle PD (NEuveden v legendě, OVĚŘIT)</t>
+        </is>
+      </c>
+      <c r="G363" s="2" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H363" s="2" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I363" s="3" t="inlineStr">
+        <is>
+          <t>průřez zásypu 3.61 m² (řez A-A) × délka 6.5 m = 23.5 m³</t>
+        </is>
+      </c>
+      <c r="J363" s="2" t="inlineStr">
+        <is>
+          <t>174101101</t>
+        </is>
+      </c>
+      <c r="K363" s="3" t="inlineStr">
+        <is>
+          <t>řez A-A — klín zásypu za S04; materiál v legendě NEuveden → OVĚŘIT</t>
+        </is>
+      </c>
+      <c r="L363" s="2" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M363" s="2" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="n">
+        <v>363</v>
+      </c>
+      <c r="B364" s="2" t="inlineStr">
+        <is>
+          <t>PSV76.003</t>
+        </is>
+      </c>
+      <c r="C364" s="2" t="inlineStr">
+        <is>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="D364" s="2" t="inlineStr">
+        <is>
+          <t>PSV-76 Zámečnické konstrukce</t>
+        </is>
+      </c>
+      <c r="E364" s="3" t="inlineStr">
+        <is>
+          <t>PSV-76 Zámečnické konstrukce</t>
+        </is>
+      </c>
+      <c r="F364" s="3" t="inlineStr">
+        <is>
+          <t>Oplocení podél vjezdu — délka dle situace, materiál OVĚŘIT (kov/dřevo neuveden)</t>
+        </is>
+      </c>
+      <c r="G364" s="2" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="H364" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I364" s="3" t="inlineStr">
+        <is>
+          <t>šířka 7775 − 4000 (posuvná vrata) = 3775 mm ≈ 3.8 bm</t>
+        </is>
+      </c>
+      <c r="J364" s="2" t="inlineStr"/>
+      <c r="K364" s="3" t="inlineStr">
+        <is>
+          <t>D.1.1.01 půdorys střechy — plot u vjezdu; materiál + přesná délka OVĚŘIT</t>
+        </is>
+      </c>
+      <c r="L364" s="2" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M364" s="2" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="n">
+        <v>364</v>
+      </c>
+      <c r="B365" s="2" t="inlineStr">
+        <is>
+          <t>PSV76.004a</t>
+        </is>
+      </c>
+      <c r="C365" s="2" t="inlineStr">
+        <is>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="D365" s="2" t="inlineStr">
+        <is>
+          <t>PSV-76 Zámečnické konstrukce</t>
+        </is>
+      </c>
+      <c r="E365" s="3" t="inlineStr">
+        <is>
+          <t>PSV-76 Zámečnické konstrukce</t>
+        </is>
+      </c>
+      <c r="F365" s="3" t="inlineStr">
+        <is>
+          <t>Montáž — Zábradlí v. 1.0 m kolem části stání — materiál OVĚŘIT (kov/dřevo neuveden)</t>
+        </is>
+      </c>
+      <c r="G365" s="2" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="H365" s="2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="I365" s="3" t="inlineStr">
+        <is>
+          <t>obvod části stání ≈ 18.5 bm (D.1.1.01), výška 1.0 m</t>
+        </is>
+      </c>
+      <c r="J365" s="2" t="inlineStr"/>
+      <c r="K365" s="3" t="inlineStr">
+        <is>
+          <t>D.1.1.01 — zábradlí 1.0 m kolem části plochy; materiál OVĚŘIT</t>
+        </is>
+      </c>
+      <c r="L365" s="2" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M365" s="2" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="n">
+        <v>365</v>
+      </c>
+      <c r="B366" s="2" t="inlineStr">
+        <is>
+          <t>PSV76.004b</t>
+        </is>
+      </c>
+      <c r="C366" s="2" t="inlineStr">
+        <is>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="D366" s="2" t="inlineStr">
+        <is>
+          <t>PSV-76 Zámečnické konstrukce</t>
+        </is>
+      </c>
+      <c r="E366" s="3" t="inlineStr">
+        <is>
+          <t>PSV-76 Zámečnické konstrukce</t>
+        </is>
+      </c>
+      <c r="F366" s="3" t="inlineStr">
+        <is>
+          <t>Dodávka — Dodávka výrobku (Zábradlí v. 1.0 m kolem části stání — materiál)</t>
+        </is>
+      </c>
+      <c r="G366" s="2" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="H366" s="2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="I366" s="3">
+        <f> montáž 1:1</f>
+        <v/>
+      </c>
+      <c r="J366" s="2" t="inlineStr"/>
+      <c r="K366" s="3" t="inlineStr">
+        <is>
+          <t>D.1.1.01 — zábradlí 1.0 m kolem části plochy; materiál OVĚŘIT</t>
+        </is>
+      </c>
+      <c r="L366" s="2" t="inlineStr">
+        <is>
+          <t>needs_lookup</t>
+        </is>
+      </c>
+      <c r="M366" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M361"/>
+  <autoFilter ref="A1:M366"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/test-data/RD_Jachymov_dum/outputs/ATOMIC_FLAT_2026-06-02.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/ATOMIC_FLAT_2026-06-02.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ATOMIC_FLAT" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ATOMIC_FLAT'!$A$1:$M$366</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ATOMIC_FLAT'!$A$1:$M$375</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M366"/>
+  <dimension ref="A1:M375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>patky horní (0.3×0.3×0.5×6 = 0.27) + zídka lemující + věnec nad patkami (odhad ~1.5 m³) = ~1.75 m³</t>
+          <t>patky horní (0.3×0.3×0.5×6 = 0.27) + věnec nad patkami 2 řady ztrac.bednění (0.5 v × 6.35 d × 0.3 š = 0.95) + zídka lemující (~0.5) = ~1.72 ≈ 1.75 m³</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>TZ statika sklad §3 + výkres D.1.1.02 (6 patek)</t>
+          <t>TZ statika sklad §3 + výkres D.1.1.02 — věnec 2 řady nad 6 patkami, šířka tvárnic 300 mm</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -5363,11 +5363,11 @@
         </is>
       </c>
       <c r="H82" s="2" t="n">
-        <v>36.74</v>
+        <v>31</v>
       </c>
       <c r="I82" s="3" t="inlineStr">
         <is>
-          <t>6.35/0.625 = 10.16 → 11 ks × 3.34 m (rozpon 3.1 + uložení) = 36.74 bm</t>
+          <t>10 ks (počítáno na výkrese D.1.1.02, rozteč 625 mm po 5850) × 3.1 m rozpon = 31 bm</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 + DXF DIMENSION</t>
+          <t>výkres D.1.1.02 — 10× trám KVH 100/160; TZ rozpon 3.1 m</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -5426,7 +5426,7 @@
         </is>
       </c>
       <c r="H83" s="2" t="n">
-        <v>40.41</v>
+        <v>34.1</v>
       </c>
       <c r="I83" s="3">
         <f> montáž × 1.10</f>
@@ -5435,7 +5435,7 @@
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 + DXF DIMENSION</t>
+          <t>výkres D.1.1.02 — 10× trám KVH 100/160; TZ rozpon 3.1 m</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
@@ -5484,21 +5484,21 @@
         </is>
       </c>
       <c r="H84" s="2" t="n">
-        <v>21.209</v>
-      </c>
-      <c r="I84" s="3">
-        <f> 21.2 m² strop skladu</f>
+        <v>18.1</v>
+      </c>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>strop skladu nad trámy = 5.85 × 3.1 = 18.1 m² (báze 10 trámů)</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>762331110</t>
+        </is>
+      </c>
+      <c r="K84" s="3">
+        <f> plocha stropu nad trámy KVH (HSV4.001)</f>
         <v/>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>762331110</t>
-        </is>
-      </c>
-      <c r="K84" s="3" t="inlineStr">
-        <is>
-          <t>TZ statika sklad §4 + DXF</t>
-        </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
@@ -5546,11 +5546,11 @@
         </is>
       </c>
       <c r="H85" s="2" t="n">
-        <v>22.26945</v>
+        <v>19</v>
       </c>
       <c r="I85" s="3" t="inlineStr">
         <is>
-          <t>21.2 × 1.05 přesah</t>
+          <t>18.1 × 1.05 přesah = 19.0 m²</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -5558,10 +5558,9 @@
           <t>712331101</t>
         </is>
       </c>
-      <c r="K85" s="3" t="inlineStr">
-        <is>
-          <t>TZ statika sklad §4 — HI souvrství</t>
-        </is>
+      <c r="K85" s="3">
+        <f> záklop (HSV4.002) × 1.05 přesah HI</f>
+        <v/>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
@@ -5609,17 +5608,16 @@
         </is>
       </c>
       <c r="H86" s="2" t="n">
-        <v>24.5</v>
+        <v>20.9</v>
       </c>
       <c r="I86" s="3">
         <f> montáž × 1.10</f>
         <v/>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
-      <c r="K86" s="3" t="inlineStr">
-        <is>
-          <t>TZ statika sklad §4 — HI souvrství</t>
-        </is>
+      <c r="K86" s="3">
+        <f> záklop (HSV4.002) × 1.05 přesah HI</f>
+        <v/>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
@@ -19523,7 +19521,7 @@
       </c>
       <c r="F326" s="3" t="inlineStr">
         <is>
-          <t>Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
+          <t>Schodiště S05 — prefabrikované betonové stupně (2× 9 stupňů 179.5×250 + mezipodesta)</t>
         </is>
       </c>
       <c r="G326" s="2" t="inlineStr">
@@ -20980,7 +20978,7 @@
       <c r="J350" s="2" t="inlineStr"/>
       <c r="K350" s="3" t="inlineStr">
         <is>
-          <t>Dodatek PD č.1 (E.01) / DI PČR požadavek</t>
+          <t>D.1.1.01 POZN 01 — zpevněná plocha betonová dlažba (= zóna napojení Dvořákova, nedupl.)</t>
         </is>
       </c>
       <c r="L350" s="2" t="inlineStr">
@@ -21037,7 +21035,7 @@
       <c r="J351" s="2" t="inlineStr"/>
       <c r="K351" s="3" t="inlineStr">
         <is>
-          <t>Dodatek PD č.1 (E.01) / DI PČR požadavek</t>
+          <t>D.1.1.01 POZN 01 — zpevněná plocha betonová dlažba (= zóna napojení Dvořákova, nedupl.)</t>
         </is>
       </c>
       <c r="L351" s="2" t="inlineStr">
@@ -21094,7 +21092,7 @@
       <c r="J352" s="2" t="inlineStr"/>
       <c r="K352" s="3" t="inlineStr">
         <is>
-          <t>Dodatek PD č.1 (E.01) / DI PČR požadavek</t>
+          <t>D.1.1.01 POZN 01 — zpevněná plocha betonová dlažba (= zóna napojení Dvořákova, nedupl.)</t>
         </is>
       </c>
       <c r="L352" s="2" t="inlineStr">
@@ -21888,8 +21886,527 @@
       </c>
       <c r="M366" s="2" t="inlineStr"/>
     </row>
+    <row r="367">
+      <c r="A367" s="2" t="n">
+        <v>366</v>
+      </c>
+      <c r="B367" s="2" t="inlineStr">
+        <is>
+          <t>HSV5.003</t>
+        </is>
+      </c>
+      <c r="C367" s="2" t="inlineStr">
+        <is>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="D367" s="2" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
+        </is>
+      </c>
+      <c r="E367" s="3" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
+        </is>
+      </c>
+      <c r="F367" s="3" t="inlineStr">
+        <is>
+          <t>Pískové lože pod dlažbu vjezdu tl. 40 mm (POZN 01)</t>
+        </is>
+      </c>
+      <c r="G367" s="2" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H367" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I367" s="3" t="inlineStr">
+        <is>
+          <t>7.0 m² × 0.04 m = 0.28 m³</t>
+        </is>
+      </c>
+      <c r="J367" s="2" t="inlineStr">
+        <is>
+          <t>564751111</t>
+        </is>
+      </c>
+      <c r="K367" s="3" t="inlineStr">
+        <is>
+          <t>D.1.1.01 POZN 01 — souvrství pod dlažbu</t>
+        </is>
+      </c>
+      <c r="L367" s="2" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M367" s="2" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="n">
+        <v>367</v>
+      </c>
+      <c r="B368" s="2" t="inlineStr">
+        <is>
+          <t>HSV5.004</t>
+        </is>
+      </c>
+      <c r="C368" s="2" t="inlineStr">
+        <is>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="D368" s="2" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
+        </is>
+      </c>
+      <c r="E368" s="3" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
+        </is>
+      </c>
+      <c r="F368" s="3" t="inlineStr">
+        <is>
+          <t>Štěrkový zhutněný podklad pod dlažbu vjezdu tl. 150 mm (POZN 01)</t>
+        </is>
+      </c>
+      <c r="G368" s="2" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H368" s="2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="I368" s="3" t="inlineStr">
+        <is>
+          <t>7.0 m² × 0.15 m = 1.05 m³</t>
+        </is>
+      </c>
+      <c r="J368" s="2" t="inlineStr">
+        <is>
+          <t>564861111</t>
+        </is>
+      </c>
+      <c r="K368" s="3" t="inlineStr">
+        <is>
+          <t>D.1.1.01 POZN 01 — souvrství pod dlažbu</t>
+        </is>
+      </c>
+      <c r="L368" s="2" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M368" s="2" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="n">
+        <v>368</v>
+      </c>
+      <c r="B369" s="2" t="inlineStr">
+        <is>
+          <t>HSV5.005</t>
+        </is>
+      </c>
+      <c r="C369" s="2" t="inlineStr">
+        <is>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="D369" s="2" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
+        </is>
+      </c>
+      <c r="E369" s="3" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
+        </is>
+      </c>
+      <c r="F369" s="3" t="inlineStr">
+        <is>
+          <t>Liniový odvodňovací žlab (prefa žlabovka š. 160 mm) podél vjezdu</t>
+        </is>
+      </c>
+      <c r="G369" s="2" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="H369" s="2" t="n">
+        <v>7.775</v>
+      </c>
+      <c r="I369" s="3" t="inlineStr">
+        <is>
+          <t>délka po hraně dlážděné plochy = 7775 mm = 7.775 bm</t>
+        </is>
+      </c>
+      <c r="J369" s="2" t="inlineStr"/>
+      <c r="K369" s="3" t="inlineStr">
+        <is>
+          <t>D.1.1.01 + detail — žlabovka 160 mm na podkl. betonu (průřez 0.06 m²)</t>
+        </is>
+      </c>
+      <c r="L369" s="2" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M369" s="2" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="n">
+        <v>369</v>
+      </c>
+      <c r="B370" s="2" t="inlineStr">
+        <is>
+          <t>HSV5.006</t>
+        </is>
+      </c>
+      <c r="C370" s="2" t="inlineStr">
+        <is>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="D370" s="2" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
+        </is>
+      </c>
+      <c r="E370" s="3" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
+        </is>
+      </c>
+      <c r="F370" s="3" t="inlineStr">
+        <is>
+          <t>Podkladní beton pod odvodňovací žlab (průřez 0.06 m²)</t>
+        </is>
+      </c>
+      <c r="G370" s="2" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H370" s="2" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="I370" s="3" t="inlineStr">
+        <is>
+          <t>0.06 m² (detail) × 7.775 m = 0.47 m³</t>
+        </is>
+      </c>
+      <c r="J370" s="2" t="inlineStr">
+        <is>
+          <t>273321411</t>
+        </is>
+      </c>
+      <c r="K370" s="3" t="inlineStr">
+        <is>
+          <t>detail řezu žlabu — průřez betonového lože 0.06 m²</t>
+        </is>
+      </c>
+      <c r="L370" s="2" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M370" s="2" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="n">
+        <v>370</v>
+      </c>
+      <c r="B371" s="2" t="inlineStr">
+        <is>
+          <t>HSV5.007</t>
+        </is>
+      </c>
+      <c r="C371" s="2" t="inlineStr">
+        <is>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="D371" s="2" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
+        </is>
+      </c>
+      <c r="E371" s="3" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
+        </is>
+      </c>
+      <c r="F371" s="3" t="inlineStr">
+        <is>
+          <t>Okapový/odvodňovací žlab na straně 6010 mm — typ OVĚŘIT</t>
+        </is>
+      </c>
+      <c r="G371" s="2" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="H371" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I371" s="3" t="inlineStr">
+        <is>
+          <t>strana 6010 mm ≈ 6.0 bm</t>
+        </is>
+      </c>
+      <c r="J371" s="2" t="inlineStr"/>
+      <c r="K371" s="3" t="inlineStr">
+        <is>
+          <t>řez — žlab na straně 6010; typ (okapový/liniový) OVĚŘIT</t>
+        </is>
+      </c>
+      <c r="L371" s="2" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M371" s="2" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="n">
+        <v>371</v>
+      </c>
+      <c r="B372" s="2" t="inlineStr">
+        <is>
+          <t>HSV1.009</t>
+        </is>
+      </c>
+      <c r="C372" s="2" t="inlineStr">
+        <is>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="D372" s="2" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
+        </is>
+      </c>
+      <c r="E372" s="3" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
+        </is>
+      </c>
+      <c r="F372" s="3" t="inlineStr">
+        <is>
+          <t>Trubka Ø ~150 mm v štěrkovém obsypu podél vysokého pasu — drenáž/odvětrání radonu (OVĚŘIT)</t>
+        </is>
+      </c>
+      <c r="G372" s="2" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="H372" s="2" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="I372" s="3" t="inlineStr">
+        <is>
+          <t>délka jako prefa stěna ≈ 6.35 m; Ø ~150 mm (měřeno z řezu, nepopsáno)</t>
+        </is>
+      </c>
+      <c r="J372" s="2" t="inlineStr"/>
+      <c r="K372" s="3" t="inlineStr">
+        <is>
+          <t>řez A-A — kroužek trubky u pasu; účel + Ø NEpopsáno → OVĚŘIT</t>
+        </is>
+      </c>
+      <c r="L372" s="2" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M372" s="2" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="n">
+        <v>372</v>
+      </c>
+      <c r="B373" s="2" t="inlineStr">
+        <is>
+          <t>HSV1.010</t>
+        </is>
+      </c>
+      <c r="C373" s="2" t="inlineStr">
+        <is>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="D373" s="2" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
+        </is>
+      </c>
+      <c r="E373" s="3" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
+        </is>
+      </c>
+      <c r="F373" s="3" t="inlineStr">
+        <is>
+          <t>Trubka Ø 120-130 mm v štěrkovém obsypu podél stěny — drenáž/odvětrání radonu (OVĚŘIT)</t>
+        </is>
+      </c>
+      <c r="G373" s="2" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="H373" s="2" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="I373" s="3" t="inlineStr">
+        <is>
+          <t>délka 6010 mm; Ø 120-130 mm (měřeno z řezu, nepopsáno)</t>
+        </is>
+      </c>
+      <c r="J373" s="2" t="inlineStr"/>
+      <c r="K373" s="3" t="inlineStr">
+        <is>
+          <t>řez — druhá trubka u pasu; účel + Ø NEpopsáno → OVĚŘIT</t>
+        </is>
+      </c>
+      <c r="L373" s="2" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M373" s="2" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="n">
+        <v>373</v>
+      </c>
+      <c r="B374" s="2" t="inlineStr">
+        <is>
+          <t>HSV5.008</t>
+        </is>
+      </c>
+      <c r="C374" s="2" t="inlineStr">
+        <is>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="D374" s="2" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
+        </is>
+      </c>
+      <c r="E374" s="3" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
+        </is>
+      </c>
+      <c r="F374" s="3" t="inlineStr">
+        <is>
+          <t>Podkladní betonová deska pod prefa schodiště S05</t>
+        </is>
+      </c>
+      <c r="G374" s="2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H374" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I374" s="3" t="inlineStr">
+        <is>
+          <t>plocha schodiště 5.5 m² (legenda) — podkladní deska</t>
+        </is>
+      </c>
+      <c r="J374" s="2" t="inlineStr">
+        <is>
+          <t>273313611</t>
+        </is>
+      </c>
+      <c r="K374" s="3" t="inlineStr">
+        <is>
+          <t>skladba S05 — podkladní betonová deska</t>
+        </is>
+      </c>
+      <c r="L374" s="2" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M374" s="2" t="inlineStr">
+        <is>
+          <t>S05_sklad</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="2" t="n">
+        <v>374</v>
+      </c>
+      <c r="B375" s="2" t="inlineStr">
+        <is>
+          <t>HSV5.009</t>
+        </is>
+      </c>
+      <c r="C375" s="2" t="inlineStr">
+        <is>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="D375" s="2" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
+        </is>
+      </c>
+      <c r="E375" s="3" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
+        </is>
+      </c>
+      <c r="F375" s="3" t="inlineStr">
+        <is>
+          <t>Kladecí vrstva ze zavlhlého betonu pod prefa stupně S05</t>
+        </is>
+      </c>
+      <c r="G375" s="2" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H375" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I375" s="3" t="inlineStr">
+        <is>
+          <t>5.5 m² × 0.05 m kladecí beton = 0.28 m³</t>
+        </is>
+      </c>
+      <c r="J375" s="2" t="inlineStr"/>
+      <c r="K375" s="3" t="inlineStr">
+        <is>
+          <t>skladba S05 — kladecí vrstva zavlhlý beton</t>
+        </is>
+      </c>
+      <c r="L375" s="2" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M375" s="2" t="inlineStr">
+        <is>
+          <t>S05_sklad</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M366"/>
+  <autoFilter ref="A1:M375"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/test-data/RD_Jachymov_dum/outputs/ATOMIC_FLAT_2026-06-02.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/ATOMIC_FLAT_2026-06-02.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ATOMIC_FLAT" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ATOMIC_FLAT'!$A$1:$M$372</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ATOMIC_FLAT'!$A$1:$M$374</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M372"/>
+  <dimension ref="A1:M374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3106,11 +3106,11 @@
         </is>
       </c>
       <c r="H45" s="2" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>patky horní (0.3×0.3×0.5×6 = 0.27) + věnec nad patkami 2 řady ztrac.bednění (0.5 v × 6.35 d × 0.3 š = 0.95) + zídka lemující (~0.5) = ~1.72 ≈ 1.75 m³</t>
+          <t>zálivka tvárnic ZB: patky horní (0.3×0.3×0.5×6=0.27) + věnec 2 řady (2×0.25 v × 0.3 š × 6.7 d=1.00) + zídka lemující (~0.5) = 1.77 m³</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>TZ statika sklad §3 + výkres D.1.1.02 — věnec 2 řady nad 6 patkami, šířka tvárnic 300 mm</t>
+          <t>TZ statika sklad §3 + výkres D.1.1.02 — věnec délka 6.7 m (ruční obmer)</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
@@ -22236,8 +22236,126 @@
         </is>
       </c>
     </row>
+    <row r="373">
+      <c r="A373" s="2" t="n">
+        <v>372</v>
+      </c>
+      <c r="B373" s="2" t="inlineStr">
+        <is>
+          <t>HSV2.007</t>
+        </is>
+      </c>
+      <c r="C373" s="2" t="inlineStr">
+        <is>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="D373" s="2" t="inlineStr">
+        <is>
+          <t>HSV-2 Základové a ŽB</t>
+        </is>
+      </c>
+      <c r="E373" s="3" t="inlineStr">
+        <is>
+          <t>HSV-2 Základové a ŽB</t>
+        </is>
+      </c>
+      <c r="F373" s="3" t="inlineStr">
+        <is>
+          <t>Bednění základových pasů + spodních patek (prostý beton) — tradiční / systémové, oboustranné kde nelze betonovat do rýhy</t>
+        </is>
+      </c>
+      <c r="G373" s="2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H373" s="2" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="I373" s="3" t="inlineStr">
+        <is>
+          <t>patky spodní 6×4×0.5×0.5=6.0 + pasy 2 strany×0.5×19.4 obvod=19.4 = 25.4 m² (část lze betonovat do rýhy → OVĚŘIT)</t>
+        </is>
+      </c>
+      <c r="J373" s="2" t="inlineStr">
+        <is>
+          <t>273351215</t>
+        </is>
+      </c>
+      <c r="K373" s="3" t="inlineStr">
+        <is>
+          <t>výkres D.1.1.02 + řez — bednění základů; podíl do rýhy vs systémové OVĚŘIT</t>
+        </is>
+      </c>
+      <c r="L373" s="2" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M373" s="2" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="n">
+        <v>373</v>
+      </c>
+      <c r="B374" s="2" t="inlineStr">
+        <is>
+          <t>HSV2.008</t>
+        </is>
+      </c>
+      <c r="C374" s="2" t="inlineStr">
+        <is>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="D374" s="2" t="inlineStr">
+        <is>
+          <t>HSV-2 Základové a ŽB</t>
+        </is>
+      </c>
+      <c r="E374" s="3" t="inlineStr">
+        <is>
+          <t>HSV-2 Základové a ŽB</t>
+        </is>
+      </c>
+      <c r="F374" s="3" t="inlineStr">
+        <is>
+          <t>Výztuž B500B vkládaná do tvárnic ztraceného bednění — patky horní (6 sloupků) + ztužující věnec nad patkami</t>
+        </is>
+      </c>
+      <c r="G374" s="2" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H374" s="2" t="n">
+        <v>153</v>
+      </c>
+      <c r="I374" s="3" t="inlineStr">
+        <is>
+          <t>zálivka tvárnic ZB 1.27 m³ (patky horní 0.27 + věnec 1.00) × 120 kg/m³ (= stěna 30 kg/m² ÷ 0.25) = 153 kg</t>
+        </is>
+      </c>
+      <c r="J374" s="2" t="inlineStr">
+        <is>
+          <t>273361821</t>
+        </is>
+      </c>
+      <c r="K374" s="3" t="inlineStr">
+        <is>
+          <t>TZ statika sklad §3 — výztuž B500B do tvárnic ZB; sazba dle stěny S03a (HSV3.003)</t>
+        </is>
+      </c>
+      <c r="L374" s="2" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M374" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M372"/>
+  <autoFilter ref="A1:M374"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>